--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/StructureDefinition-at-prenudge-questionnaireresponse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T07:28:06+00:00</t>
+    <t>2026-10-21T09:39:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -473,7 +473,7 @@
 </t>
   </si>
   <si>
-    <t>Mandatory date the answers were gathered</t>
+    <t>Unique id for this set of answers, at least one is assigned by the data provider</t>
   </si>
   <si>
     <t>A business identifier assigned to a particular completed (or partially completed) questionnaire.</t>
@@ -756,7 +756,7 @@
     <t>QuestionnaireResponse.status</t>
   </si>
   <si>
-    <t>In PreNUDGE only completed QuestionnaireResponses are beeing accepted</t>
+    <t>In PreNUDGE only completed QuestionnaireResponses are being accepted</t>
   </si>
   <si>
     <t>The position of the questionnaire response within its overall lifecycle.</t>
@@ -857,7 +857,7 @@
 </t>
   </si>
   <si>
-    <t>Date the answers were gathered</t>
+    <t>Mandatory date the answers were gathered</t>
   </si>
   <si>
     <t>The date and/or time that this set of answers were last changed.</t>
